--- a/call-list/私立高校_架電リスト_東京都.xlsx
+++ b/call-list/私立高校_架電リスト_東京都.xlsx
@@ -12,7 +12,7 @@
     <sheet name="使い方・注意事項" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$244</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'架電リスト'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O204"/>
+  <dimension ref="A1:O244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>私立高等学校 架電リスト（東京都／200校）</t>
+          <t>私立高等学校 架電リスト（東京都／240校）</t>
         </is>
       </c>
     </row>
@@ -12480,9 +12480,2357 @@
         </is>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" s="4" t="n">
+        <v>201</v>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>文京区</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>文京学院大学女子高等学校</t>
+        </is>
+      </c>
+      <c r="E205" s="6" t="inlineStr">
+        <is>
+          <t>03-3946-5301</t>
+        </is>
+      </c>
+      <c r="F205" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G205" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H205" s="8" t="n"/>
+      <c r="I205" s="9" t="n"/>
+      <c r="J205" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K205" s="8" t="n"/>
+      <c r="L205" s="9" t="n"/>
+      <c r="M205" s="10" t="inlineStr">
+        <is>
+          <t>中高共通</t>
+        </is>
+      </c>
+      <c r="N205" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/259 ; https://www.bgu.ac.jp/bgu_sys/wp-content/uploads/2026/02/bgu815.pdf</t>
+        </is>
+      </c>
+      <c r="O205" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="n">
+        <v>202</v>
+      </c>
+      <c r="B206" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="inlineStr">
+        <is>
+          <t>品川区</t>
+        </is>
+      </c>
+      <c r="D206" s="5" t="inlineStr">
+        <is>
+          <t>文教大学付属高等学校</t>
+        </is>
+      </c>
+      <c r="E206" s="6" t="inlineStr">
+        <is>
+          <t>03-3783-5511</t>
+        </is>
+      </c>
+      <c r="F206" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G206" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H206" s="8" t="n"/>
+      <c r="I206" s="9" t="n"/>
+      <c r="J206" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K206" s="8" t="n"/>
+      <c r="L206" s="9" t="n"/>
+      <c r="M206" s="10" t="inlineStr">
+        <is>
+          <t>公式資料に「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N206" s="11" t="inlineStr">
+        <is>
+          <t>https://www.bunkyo.ac.jp/jsh/news/docs/2020hennyu_02.pdf</t>
+        </is>
+      </c>
+      <c r="O206" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="n">
+        <v>203</v>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="inlineStr">
+        <is>
+          <t>三鷹市</t>
+        </is>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>法政大学高等学校</t>
+        </is>
+      </c>
+      <c r="E207" s="6" t="inlineStr">
+        <is>
+          <t>0422-79-6230</t>
+        </is>
+      </c>
+      <c r="F207" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G207" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H207" s="8" t="n"/>
+      <c r="I207" s="9" t="n"/>
+      <c r="J207" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K207" s="8" t="n"/>
+      <c r="L207" s="9" t="n"/>
+      <c r="M207" s="10" t="inlineStr">
+        <is>
+          <t>中高共通</t>
+        </is>
+      </c>
+      <c r="N207" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22040140 ; https://www.inter-edu.com/schools/school/2007</t>
+        </is>
+      </c>
+      <c r="O207" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="n">
+        <v>204</v>
+      </c>
+      <c r="B208" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="inlineStr">
+        <is>
+          <t>中野区</t>
+        </is>
+      </c>
+      <c r="D208" s="5" t="inlineStr">
+        <is>
+          <t>宝仙学園高等学校女子部</t>
+        </is>
+      </c>
+      <c r="E208" s="6" t="inlineStr">
+        <is>
+          <t>03-3371-7103</t>
+        </is>
+      </c>
+      <c r="F208" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G208" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H208" s="8" t="n"/>
+      <c r="I208" s="9" t="n"/>
+      <c r="J208" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K208" s="8" t="n"/>
+      <c r="L208" s="9" t="n"/>
+      <c r="M208" s="10" t="inlineStr">
+        <is>
+          <t>学校ネットの一覧に区名がなく、所在地は中野区（中央2-28-3）として調査。理数インターと同じ番号（同じ敷地）</t>
+        </is>
+      </c>
+      <c r="N208" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/681</t>
+        </is>
+      </c>
+      <c r="O208" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="B209" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C209" s="5" t="inlineStr">
+        <is>
+          <t>中野区</t>
+        </is>
+      </c>
+      <c r="D209" s="5" t="inlineStr">
+        <is>
+          <t>宝仙学園 順天堂大学系属理数インター高等学校</t>
+        </is>
+      </c>
+      <c r="E209" s="6" t="inlineStr">
+        <is>
+          <t>03-3371-7103</t>
+        </is>
+      </c>
+      <c r="F209" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G209" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H209" s="8" t="n"/>
+      <c r="I209" s="9" t="n"/>
+      <c r="J209" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K209" s="8" t="n"/>
+      <c r="L209" s="9" t="n"/>
+      <c r="M209" s="10" t="inlineStr">
+        <is>
+          <t>中高共通。宝仙学園女子部と同じ番号</t>
+        </is>
+      </c>
+      <c r="N209" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/95</t>
+        </is>
+      </c>
+      <c r="O209" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="n">
+        <v>206</v>
+      </c>
+      <c r="B210" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>豊島区</t>
+        </is>
+      </c>
+      <c r="D210" s="5" t="inlineStr">
+        <is>
+          <t>豊南高等学校</t>
+        </is>
+      </c>
+      <c r="E210" s="6" t="inlineStr">
+        <is>
+          <t>03-3959-5511</t>
+        </is>
+      </c>
+      <c r="F210" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G210" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H210" s="8" t="n"/>
+      <c r="I210" s="9" t="n"/>
+      <c r="J210" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K210" s="8" t="n"/>
+      <c r="L210" s="9" t="n"/>
+      <c r="M210" s="10" t="inlineStr">
+        <is>
+          <t>学校情報サイト1件のみで確認</t>
+        </is>
+      </c>
+      <c r="N210" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/682</t>
+        </is>
+      </c>
+      <c r="O210" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="n">
+        <v>207</v>
+      </c>
+      <c r="B211" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t>品川区</t>
+        </is>
+      </c>
+      <c r="D211" s="5" t="inlineStr">
+        <is>
+          <t>朋優学院高等学校</t>
+        </is>
+      </c>
+      <c r="E211" s="6" t="inlineStr">
+        <is>
+          <t>03-3784-2131</t>
+        </is>
+      </c>
+      <c r="F211" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G211" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H211" s="8" t="n"/>
+      <c r="I211" s="9" t="n"/>
+      <c r="J211" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K211" s="8" t="n"/>
+      <c r="L211" s="9" t="n"/>
+      <c r="M211" s="10" t="inlineStr">
+        <is>
+          <t>2つの情報源で一致</t>
+        </is>
+      </c>
+      <c r="N211" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/680 ; https://www.univpress.co.jp/gk_pdf/13614.pdf</t>
+        </is>
+      </c>
+      <c r="O211" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="n">
+        <v>208</v>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t>新宿区</t>
+        </is>
+      </c>
+      <c r="D212" s="5" t="inlineStr">
+        <is>
+          <t>保善高等学校</t>
+        </is>
+      </c>
+      <c r="E212" s="6" t="inlineStr">
+        <is>
+          <t>03-3209-8756</t>
+        </is>
+      </c>
+      <c r="F212" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G212" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H212" s="8" t="n"/>
+      <c r="I212" s="9" t="n"/>
+      <c r="J212" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K212" s="8" t="n"/>
+      <c r="L212" s="9" t="n"/>
+      <c r="M212" s="10" t="inlineStr">
+        <is>
+          <t>学校情報サイト1件のみで確認</t>
+        </is>
+      </c>
+      <c r="N212" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/679</t>
+        </is>
+      </c>
+      <c r="O212" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="n">
+        <v>209</v>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>中野区</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
+        <is>
+          <t>堀越高等学校</t>
+        </is>
+      </c>
+      <c r="E213" s="6" t="inlineStr">
+        <is>
+          <t>03-3363-7661</t>
+        </is>
+      </c>
+      <c r="F213" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H213" s="8" t="n"/>
+      <c r="I213" s="9" t="n"/>
+      <c r="J213" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K213" s="8" t="n"/>
+      <c r="L213" s="9" t="n"/>
+      <c r="M213" s="10" t="inlineStr">
+        <is>
+          <t>代表として掲載</t>
+        </is>
+      </c>
+      <c r="N213" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/1929 ; https://school.js88.com/scl_h/22039490?page=8</t>
+        </is>
+      </c>
+      <c r="O213" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="B214" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>豊島区</t>
+        </is>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
+        <is>
+          <t>本郷高等学校</t>
+        </is>
+      </c>
+      <c r="E214" s="6" t="inlineStr">
+        <is>
+          <t>03-3917-1456</t>
+        </is>
+      </c>
+      <c r="F214" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G214" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H214" s="8" t="n"/>
+      <c r="I214" s="9" t="n"/>
+      <c r="J214" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K214" s="8" t="n"/>
+      <c r="L214" s="9" t="n"/>
+      <c r="M214" s="10" t="inlineStr">
+        <is>
+          <t>中高共通</t>
+        </is>
+      </c>
+      <c r="N214" s="11" t="inlineStr">
+        <is>
+          <t>https://www.minkou.jp/hischool/school/university/4472/s=1/ ; https://www.inter-edu.com/schools/school/82/</t>
+        </is>
+      </c>
+      <c r="O214" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="n">
+        <v>211</v>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>世田谷区</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
+        <is>
+          <t>三田国際科学学園高等学校</t>
+        </is>
+      </c>
+      <c r="E215" s="6" t="inlineStr">
+        <is>
+          <t>03-3707-5676</t>
+        </is>
+      </c>
+      <c r="F215" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H215" s="8" t="n"/>
+      <c r="I215" s="9" t="n"/>
+      <c r="J215" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K215" s="8" t="n"/>
+      <c r="L215" s="9" t="n"/>
+      <c r="M215" s="10" t="inlineStr">
+        <is>
+          <t>【校名変更】2025年4月に三田国際学園から改称。中高共通</t>
+        </is>
+      </c>
+      <c r="N215" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/252</t>
+        </is>
+      </c>
+      <c r="O215" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="n">
+        <v>212</v>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>三鷹市</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
+        <is>
+          <t>明星学園高等学校</t>
+        </is>
+      </c>
+      <c r="E216" s="14" t="n"/>
+      <c r="F216" s="15" t="inlineStr">
+        <is>
+          <t>要調査</t>
+        </is>
+      </c>
+      <c r="G216" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H216" s="8" t="n"/>
+      <c r="I216" s="9" t="n"/>
+      <c r="J216" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K216" s="8" t="n"/>
+      <c r="L216" s="9" t="n"/>
+      <c r="M216" s="10" t="inlineStr">
+        <is>
+          <t>情報源で番号が食い違い。候補：0422-43-2196（中高共通として複数サイト）／0422-48-6221。明星高校（府中市）とは別の学校</t>
+        </is>
+      </c>
+      <c r="N216" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/146 ; https://school.js88.com/scl_h/22040160</t>
+        </is>
+      </c>
+      <c r="O216" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="n">
+        <v>213</v>
+      </c>
+      <c r="B217" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>千代田区</t>
+        </is>
+      </c>
+      <c r="D217" s="5" t="inlineStr">
+        <is>
+          <t>三輪田学園高等学校</t>
+        </is>
+      </c>
+      <c r="E217" s="6" t="inlineStr">
+        <is>
+          <t>03-3263-7801</t>
+        </is>
+      </c>
+      <c r="F217" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G217" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H217" s="8" t="n"/>
+      <c r="I217" s="9" t="n"/>
+      <c r="J217" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K217" s="8" t="n"/>
+      <c r="L217" s="9" t="n"/>
+      <c r="M217" s="10" t="inlineStr">
+        <is>
+          <t>中高共通</t>
+        </is>
+      </c>
+      <c r="N217" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/70 ; https://www.minkou.jp/junior/school/7488/</t>
+        </is>
+      </c>
+      <c r="O217" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="n">
+        <v>214</v>
+      </c>
+      <c r="B218" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="inlineStr">
+        <is>
+          <t>練馬区</t>
+        </is>
+      </c>
+      <c r="D218" s="5" t="inlineStr">
+        <is>
+          <t>武蔵高等学校</t>
+        </is>
+      </c>
+      <c r="E218" s="6" t="inlineStr">
+        <is>
+          <t>03-5984-3741</t>
+        </is>
+      </c>
+      <c r="F218" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G218" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H218" s="8" t="n"/>
+      <c r="I218" s="9" t="n"/>
+      <c r="J218" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K218" s="8" t="n"/>
+      <c r="L218" s="9" t="n"/>
+      <c r="M218" s="10" t="inlineStr">
+        <is>
+          <t>中高共通。高校募集なし（完全中高一貫）。武蔵野高校とは別の学校</t>
+        </is>
+      </c>
+      <c r="N218" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/18</t>
+        </is>
+      </c>
+      <c r="O218" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="B219" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C219" s="5" t="inlineStr">
+        <is>
+          <t>北区</t>
+        </is>
+      </c>
+      <c r="D219" s="5" t="inlineStr">
+        <is>
+          <t>武蔵野高等学校</t>
+        </is>
+      </c>
+      <c r="E219" s="6" t="inlineStr">
+        <is>
+          <t>03-3910-0151</t>
+        </is>
+      </c>
+      <c r="F219" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G219" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H219" s="8" t="n"/>
+      <c r="I219" s="9" t="n"/>
+      <c r="J219" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K219" s="8" t="n"/>
+      <c r="L219" s="9" t="n"/>
+      <c r="M219" s="10" t="inlineStr">
+        <is>
+          <t>北区の学校。武蔵高校・武蔵野大学高校とは別の学校</t>
+        </is>
+      </c>
+      <c r="N219" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/291 ; https://school.js88.com/scl_h/22038770?page=5</t>
+        </is>
+      </c>
+      <c r="O219" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="n">
+        <v>216</v>
+      </c>
+      <c r="B220" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C220" s="5" t="inlineStr">
+        <is>
+          <t>西東京市</t>
+        </is>
+      </c>
+      <c r="D220" s="5" t="inlineStr">
+        <is>
+          <t>武蔵野大学高等学校</t>
+        </is>
+      </c>
+      <c r="E220" s="6" t="inlineStr">
+        <is>
+          <t>042-468-3256</t>
+        </is>
+      </c>
+      <c r="F220" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G220" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H220" s="8" t="n"/>
+      <c r="I220" s="9" t="n"/>
+      <c r="J220" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K220" s="8" t="n"/>
+      <c r="L220" s="9" t="n"/>
+      <c r="M220" s="10" t="inlineStr">
+        <is>
+          <t>中高共通</t>
+        </is>
+      </c>
+      <c r="N220" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/1976</t>
+        </is>
+      </c>
+      <c r="O220" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="n">
+        <v>217</v>
+      </c>
+      <c r="B221" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C221" s="5" t="inlineStr">
+        <is>
+          <t>港区</t>
+        </is>
+      </c>
+      <c r="D221" s="5" t="inlineStr">
+        <is>
+          <t>明治学院高等学校</t>
+        </is>
+      </c>
+      <c r="E221" s="6" t="inlineStr">
+        <is>
+          <t>03-5421-5011</t>
+        </is>
+      </c>
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G221" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H221" s="8" t="n"/>
+      <c r="I221" s="9" t="n"/>
+      <c r="J221" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K221" s="8" t="n"/>
+      <c r="L221" s="9" t="n"/>
+      <c r="M221" s="10" t="inlineStr">
+        <is>
+          <t>代表として掲載</t>
+        </is>
+      </c>
+      <c r="N221" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22038230/</t>
+        </is>
+      </c>
+      <c r="O221" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="n">
+        <v>218</v>
+      </c>
+      <c r="B222" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C222" s="5" t="inlineStr">
+        <is>
+          <t>東村山市</t>
+        </is>
+      </c>
+      <c r="D222" s="5" t="inlineStr">
+        <is>
+          <t>明治学院東村山高等学校</t>
+        </is>
+      </c>
+      <c r="E222" s="6" t="inlineStr">
+        <is>
+          <t>042-391-2142</t>
+        </is>
+      </c>
+      <c r="F222" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G222" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H222" s="8" t="n"/>
+      <c r="I222" s="9" t="n"/>
+      <c r="J222" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K222" s="8" t="n"/>
+      <c r="L222" s="9" t="n"/>
+      <c r="M222" s="10" t="inlineStr">
+        <is>
+          <t>明治学院中学校と共通</t>
+        </is>
+      </c>
+      <c r="N222" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/144 ; https://school.js88.com/scl_h/22040060?page=5</t>
+        </is>
+      </c>
+      <c r="O222" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="n">
+        <v>219</v>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>世田谷区</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>明治大学付属世田谷高等学校</t>
+        </is>
+      </c>
+      <c r="E223" s="6" t="inlineStr">
+        <is>
+          <t>03-3322-6331</t>
+        </is>
+      </c>
+      <c r="F223" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G223" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H223" s="8" t="n"/>
+      <c r="I223" s="9" t="n"/>
+      <c r="J223" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K223" s="8" t="n"/>
+      <c r="L223" s="9" t="n"/>
+      <c r="M223" s="10" t="inlineStr">
+        <is>
+          <t>【校名変更】旧 日本学園高校（2026年4月に改称）</t>
+        </is>
+      </c>
+      <c r="N223" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/2042</t>
+        </is>
+      </c>
+      <c r="O223" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="B224" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C224" s="5" t="inlineStr">
+        <is>
+          <t>中野区</t>
+        </is>
+      </c>
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>明治大学付属中野高等学校</t>
+        </is>
+      </c>
+      <c r="E224" s="6" t="inlineStr">
+        <is>
+          <t>03-3362-8704</t>
+        </is>
+      </c>
+      <c r="F224" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G224" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H224" s="8" t="n"/>
+      <c r="I224" s="9" t="n"/>
+      <c r="J224" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K224" s="8" t="n"/>
+      <c r="L224" s="9" t="n"/>
+      <c r="M224" s="10" t="inlineStr">
+        <is>
+          <t>中高共通</t>
+        </is>
+      </c>
+      <c r="N224" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/1948</t>
+        </is>
+      </c>
+      <c r="O224" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="n">
+        <v>221</v>
+      </c>
+      <c r="B225" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C225" s="5" t="inlineStr">
+        <is>
+          <t>八王子市</t>
+        </is>
+      </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>明治大学付属八王子高等学校</t>
+        </is>
+      </c>
+      <c r="E225" s="6" t="inlineStr">
+        <is>
+          <t>042-691-0321</t>
+        </is>
+      </c>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G225" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H225" s="8" t="n"/>
+      <c r="I225" s="9" t="n"/>
+      <c r="J225" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K225" s="8" t="n"/>
+      <c r="L225" s="9" t="n"/>
+      <c r="M225" s="10" t="inlineStr">
+        <is>
+          <t>2024年に「明治大学付属中野八王子」から改称。複数サイトで一致</t>
+        </is>
+      </c>
+      <c r="N225" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/1967</t>
+        </is>
+      </c>
+      <c r="O225" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="n">
+        <v>222</v>
+      </c>
+      <c r="B226" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C226" s="5" t="inlineStr">
+        <is>
+          <t>調布市</t>
+        </is>
+      </c>
+      <c r="D226" s="5" t="inlineStr">
+        <is>
+          <t>明治大学付属明治高等学校</t>
+        </is>
+      </c>
+      <c r="E226" s="6" t="inlineStr">
+        <is>
+          <t>042-444-9100</t>
+        </is>
+      </c>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G226" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H226" s="8" t="n"/>
+      <c r="I226" s="9" t="n"/>
+      <c r="J226" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K226" s="8" t="n"/>
+      <c r="L226" s="9" t="n"/>
+      <c r="M226" s="10" t="inlineStr">
+        <is>
+          <t>中高共通。公式資料の事務室の番号（新しい公式資料には042-444-9101の記載もあり）</t>
+        </is>
+      </c>
+      <c r="N226" s="11" t="inlineStr">
+        <is>
+          <t>https://www.meiji.ac.jp/ko_chu/admission/ujnu1b0000000aab-att/a1568003491541.pdf ; https://school.js88.com/scl_h/22038060</t>
+        </is>
+      </c>
+      <c r="O226" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="n">
+        <v>223</v>
+      </c>
+      <c r="B227" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C227" s="5" t="inlineStr">
+        <is>
+          <t>府中市</t>
+        </is>
+      </c>
+      <c r="D227" s="5" t="inlineStr">
+        <is>
+          <t>明星高等学校（東京都）</t>
+        </is>
+      </c>
+      <c r="E227" s="6" t="inlineStr">
+        <is>
+          <t>042-368-5201</t>
+        </is>
+      </c>
+      <c r="F227" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G227" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H227" s="8" t="n"/>
+      <c r="I227" s="9" t="n"/>
+      <c r="J227" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K227" s="8" t="n"/>
+      <c r="L227" s="9" t="n"/>
+      <c r="M227" s="10" t="inlineStr">
+        <is>
+          <t>中高共通。府中市の学校で、明星学園（三鷹市）とは別の学校</t>
+        </is>
+      </c>
+      <c r="N227" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/2009</t>
+        </is>
+      </c>
+      <c r="O227" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="n">
+        <v>224</v>
+      </c>
+      <c r="B228" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C228" s="5" t="inlineStr">
+        <is>
+          <t>東村山市</t>
+        </is>
+      </c>
+      <c r="D228" s="5" t="inlineStr">
+        <is>
+          <t>明法高等学校</t>
+        </is>
+      </c>
+      <c r="E228" s="6" t="inlineStr">
+        <is>
+          <t>042-393-5611</t>
+        </is>
+      </c>
+      <c r="F228" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G228" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H228" s="8" t="n"/>
+      <c r="I228" s="9" t="n"/>
+      <c r="J228" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K228" s="8" t="n"/>
+      <c r="L228" s="9" t="n"/>
+      <c r="M228" s="10" t="inlineStr">
+        <is>
+          <t>中高共通。複数ページで一致</t>
+        </is>
+      </c>
+      <c r="N228" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/1981</t>
+        </is>
+      </c>
+      <c r="O228" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="B229" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C229" s="5" t="inlineStr">
+        <is>
+          <t>目黒区</t>
+        </is>
+      </c>
+      <c r="D229" s="5" t="inlineStr">
+        <is>
+          <t>目黒学院高等学校</t>
+        </is>
+      </c>
+      <c r="E229" s="6" t="inlineStr">
+        <is>
+          <t>03-3711-6556</t>
+        </is>
+      </c>
+      <c r="F229" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G229" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H229" s="8" t="n"/>
+      <c r="I229" s="9" t="n"/>
+      <c r="J229" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K229" s="8" t="n"/>
+      <c r="L229" s="9" t="n"/>
+      <c r="M229" s="10" t="inlineStr">
+        <is>
+          <t>複数サイトで一致</t>
+        </is>
+      </c>
+      <c r="N229" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/193</t>
+        </is>
+      </c>
+      <c r="O229" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="n">
+        <v>226</v>
+      </c>
+      <c r="B230" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C230" s="5" t="inlineStr">
+        <is>
+          <t>目黒区</t>
+        </is>
+      </c>
+      <c r="D230" s="5" t="inlineStr">
+        <is>
+          <t>目黒日本大学高等学校</t>
+        </is>
+      </c>
+      <c r="E230" s="6" t="inlineStr">
+        <is>
+          <t>03-3492-3388</t>
+        </is>
+      </c>
+      <c r="F230" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G230" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H230" s="8" t="n"/>
+      <c r="I230" s="9" t="n"/>
+      <c r="J230" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K230" s="8" t="n"/>
+      <c r="L230" s="9" t="n"/>
+      <c r="M230" s="10" t="inlineStr">
+        <is>
+          <t>全日制の番号。通信制課程は03-3492-6674。2019年に日出高校から改称</t>
+        </is>
+      </c>
+      <c r="N230" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/2107 ; https://www.univpress.co.jp/gk_pdf/13623.pdf</t>
+        </is>
+      </c>
+      <c r="O230" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="B231" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C231" s="5" t="inlineStr">
+        <is>
+          <t>新宿区</t>
+        </is>
+      </c>
+      <c r="D231" s="5" t="inlineStr">
+        <is>
+          <t>目白研心高等学校</t>
+        </is>
+      </c>
+      <c r="E231" s="6" t="inlineStr">
+        <is>
+          <t>03-5996-3133</t>
+        </is>
+      </c>
+      <c r="F231" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G231" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H231" s="8" t="n"/>
+      <c r="I231" s="9" t="n"/>
+      <c r="J231" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K231" s="8" t="n"/>
+      <c r="L231" s="9" t="n"/>
+      <c r="M231" s="10" t="inlineStr">
+        <is>
+          <t>広報部の番号とするサイトあり。代表は03-5996-3131の可能性</t>
+        </is>
+      </c>
+      <c r="N231" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/2011 ; https://school.js88.com/scl_h/22038300</t>
+        </is>
+      </c>
+      <c r="O231" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="n">
+        <v>228</v>
+      </c>
+      <c r="B232" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C232" s="5" t="inlineStr">
+        <is>
+          <t>目黒区</t>
+        </is>
+      </c>
+      <c r="D232" s="5" t="inlineStr">
+        <is>
+          <t>八雲学園高等学校</t>
+        </is>
+      </c>
+      <c r="E232" s="6" t="inlineStr">
+        <is>
+          <t>03-3717-1196</t>
+        </is>
+      </c>
+      <c r="F232" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G232" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H232" s="8" t="n"/>
+      <c r="I232" s="9" t="n"/>
+      <c r="J232" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K232" s="8" t="n"/>
+      <c r="L232" s="9" t="n"/>
+      <c r="M232" s="10" t="inlineStr">
+        <is>
+          <t>中高共通</t>
+        </is>
+      </c>
+      <c r="N232" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/2084</t>
+        </is>
+      </c>
+      <c r="O232" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="n">
+        <v>229</v>
+      </c>
+      <c r="B233" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C233" s="5" t="inlineStr">
+        <is>
+          <t>墨田区</t>
+        </is>
+      </c>
+      <c r="D233" s="5" t="inlineStr">
+        <is>
+          <t>安田学園高等学校</t>
+        </is>
+      </c>
+      <c r="E233" s="6" t="inlineStr">
+        <is>
+          <t>03-3624-2666</t>
+        </is>
+      </c>
+      <c r="F233" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G233" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H233" s="8" t="n"/>
+      <c r="I233" s="9" t="n"/>
+      <c r="J233" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K233" s="8" t="n"/>
+      <c r="L233" s="9" t="n"/>
+      <c r="M233" s="10" t="inlineStr">
+        <is>
+          <t>公式資料に「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N233" s="11" t="inlineStr">
+        <is>
+          <t>https://www.yasuda.ed.jp/wordpress/wp-content/uploads/2025/09/20250922-68d0e3d53964f.pdf</t>
+        </is>
+      </c>
+      <c r="O233" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="n">
+        <v>230</v>
+      </c>
+      <c r="B234" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C234" s="5" t="inlineStr">
+        <is>
+          <t>港区</t>
+        </is>
+      </c>
+      <c r="D234" s="5" t="inlineStr">
+        <is>
+          <t>山脇学園高等学校</t>
+        </is>
+      </c>
+      <c r="E234" s="6" t="inlineStr">
+        <is>
+          <t>03-3585-3911</t>
+        </is>
+      </c>
+      <c r="F234" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G234" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H234" s="8" t="n"/>
+      <c r="I234" s="9" t="n"/>
+      <c r="J234" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K234" s="8" t="n"/>
+      <c r="L234" s="9" t="n"/>
+      <c r="M234" s="10" t="inlineStr">
+        <is>
+          <t>中高共通。公式資料で確認</t>
+        </is>
+      </c>
+      <c r="N234" s="11" t="inlineStr">
+        <is>
+          <t>https://www.yamawaki.ed.jp/wordpress/wp-content/uploads/2025/07/2026yamawaki_youkou_ippan.pdf ; https://www.inter-edu.com/schools/school/261</t>
+        </is>
+      </c>
+      <c r="O234" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="n">
+        <v>231</v>
+      </c>
+      <c r="B235" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C235" s="5" t="inlineStr">
+        <is>
+          <t>豊島区</t>
+        </is>
+      </c>
+      <c r="D235" s="5" t="inlineStr">
+        <is>
+          <t>立教池袋高等学校</t>
+        </is>
+      </c>
+      <c r="E235" s="6" t="inlineStr">
+        <is>
+          <t>03-3985-2707</t>
+        </is>
+      </c>
+      <c r="F235" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G235" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H235" s="8" t="n"/>
+      <c r="I235" s="9" t="n"/>
+      <c r="J235" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K235" s="8" t="n"/>
+      <c r="L235" s="9" t="n"/>
+      <c r="M235" s="10" t="inlineStr">
+        <is>
+          <t>中高共通</t>
+        </is>
+      </c>
+      <c r="N235" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/2043</t>
+        </is>
+      </c>
+      <c r="O235" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="n">
+        <v>232</v>
+      </c>
+      <c r="B236" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C236" s="5" t="inlineStr">
+        <is>
+          <t>豊島区</t>
+        </is>
+      </c>
+      <c r="D236" s="5" t="inlineStr">
+        <is>
+          <t>立教英国学院高等部</t>
+        </is>
+      </c>
+      <c r="E236" s="14" t="n"/>
+      <c r="F236" s="15" t="inlineStr">
+        <is>
+          <t>要調査</t>
+        </is>
+      </c>
+      <c r="G236" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H236" s="8" t="n"/>
+      <c r="I236" s="9" t="n"/>
+      <c r="J236" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K236" s="8" t="n"/>
+      <c r="L236" s="9" t="n"/>
+      <c r="M236" s="10" t="inlineStr">
+        <is>
+          <t>学校本体は英国。東京事務所（立教学院内）の番号として03-3985-2785が1サイトに掲載。公式の問い合わせ先は英国の番号</t>
+        </is>
+      </c>
+      <c r="N236" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gakkou.net/chugaku/view/index_227851.html</t>
+        </is>
+      </c>
+      <c r="O236" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="n">
+        <v>233</v>
+      </c>
+      <c r="B237" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C237" s="5" t="inlineStr">
+        <is>
+          <t>杉並区</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="inlineStr">
+        <is>
+          <t>立教女学院高等学校</t>
+        </is>
+      </c>
+      <c r="E237" s="6" t="inlineStr">
+        <is>
+          <t>03-3334-5103</t>
+        </is>
+      </c>
+      <c r="F237" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G237" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H237" s="8" t="n"/>
+      <c r="I237" s="9" t="n"/>
+      <c r="J237" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K237" s="8" t="n"/>
+      <c r="L237" s="9" t="n"/>
+      <c r="M237" s="10" t="inlineStr">
+        <is>
+          <t>中高共通。杉並区の一覧で確認</t>
+        </is>
+      </c>
+      <c r="N237" s="11" t="inlineStr">
+        <is>
+          <t>https://www.city.suginami.tokyo.jp/shisetsu/school/shiritsuko/index.html</t>
+        </is>
+      </c>
+      <c r="O237" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="n">
+        <v>234</v>
+      </c>
+      <c r="B238" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C238" s="5" t="inlineStr">
+        <is>
+          <t>墨田区</t>
+        </is>
+      </c>
+      <c r="D238" s="5" t="inlineStr">
+        <is>
+          <t>立志舎高等学校</t>
+        </is>
+      </c>
+      <c r="E238" s="6" t="inlineStr">
+        <is>
+          <t>03-5608-1033</t>
+        </is>
+      </c>
+      <c r="F238" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G238" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H238" s="8" t="n"/>
+      <c r="I238" s="9" t="n"/>
+      <c r="J238" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K238" s="8" t="n"/>
+      <c r="L238" s="9" t="n"/>
+      <c r="M238" s="10" t="inlineStr">
+        <is>
+          <t>通信制。東京都の通信制一覧のみで確認</t>
+        </is>
+      </c>
+      <c r="N238" s="11" t="inlineStr">
+        <is>
+          <t>https://www.seikatubunka.metro.tokyo.lg.jp/documents/d/seikatubunka/13high_tushin_r61201</t>
+        </is>
+      </c>
+      <c r="O238" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="B239" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C239" s="5" t="inlineStr">
+        <is>
+          <t>大田区</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
+        <is>
+          <t>立正大学付属立正高等学校</t>
+        </is>
+      </c>
+      <c r="E239" s="6" t="inlineStr">
+        <is>
+          <t>03-6303-7683</t>
+        </is>
+      </c>
+      <c r="F239" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G239" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H239" s="8" t="n"/>
+      <c r="I239" s="9" t="n"/>
+      <c r="J239" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K239" s="8" t="n"/>
+      <c r="L239" s="9" t="n"/>
+      <c r="M239" s="10" t="inlineStr">
+        <is>
+          <t>中高共通。公式の学校案内で確認</t>
+        </is>
+      </c>
+      <c r="N239" s="11" t="inlineStr">
+        <is>
+          <t>https://www.rissho-hs.ac.jp/material/data/request/RisshoJHguide2026.pdf</t>
+        </is>
+      </c>
+      <c r="O239" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="n">
+        <v>236</v>
+      </c>
+      <c r="B240" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C240" s="5" t="inlineStr">
+        <is>
+          <t>町田市</t>
+        </is>
+      </c>
+      <c r="D240" s="5" t="inlineStr">
+        <is>
+          <t>和光高等学校</t>
+        </is>
+      </c>
+      <c r="E240" s="14" t="n"/>
+      <c r="F240" s="15" t="inlineStr">
+        <is>
+          <t>要調査</t>
+        </is>
+      </c>
+      <c r="G240" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H240" s="8" t="n"/>
+      <c r="I240" s="9" t="n"/>
+      <c r="J240" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K240" s="8" t="n"/>
+      <c r="L240" s="9" t="n"/>
+      <c r="M240" s="10" t="inlineStr">
+        <is>
+          <t>情報源で番号が食い違い。候補：042-734-3401（代表とする情報あり）／042-734-3402／042-734-3403</t>
+        </is>
+      </c>
+      <c r="N240" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22039400 ; https://www.inter-edu.com/schools/school/2012</t>
+        </is>
+      </c>
+      <c r="O240" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="n">
+        <v>237</v>
+      </c>
+      <c r="B241" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C241" s="5" t="inlineStr">
+        <is>
+          <t>新宿区</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="inlineStr">
+        <is>
+          <t>早稲田高等学校</t>
+        </is>
+      </c>
+      <c r="E241" s="6" t="inlineStr">
+        <is>
+          <t>03-3202-7674</t>
+        </is>
+      </c>
+      <c r="F241" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G241" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H241" s="8" t="n"/>
+      <c r="I241" s="9" t="n"/>
+      <c r="J241" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K241" s="8" t="n"/>
+      <c r="L241" s="9" t="n"/>
+      <c r="M241" s="10" t="inlineStr">
+        <is>
+          <t>中高共通</t>
+        </is>
+      </c>
+      <c r="N241" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22038310 ; https://www.inter-edu.com/schools/school/22</t>
+        </is>
+      </c>
+      <c r="O241" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="n">
+        <v>238</v>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t>国分寺市</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
+        <is>
+          <t>早稲田実業学校高等部</t>
+        </is>
+      </c>
+      <c r="E242" s="6" t="inlineStr">
+        <is>
+          <t>042-300-2121</t>
+        </is>
+      </c>
+      <c r="F242" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G242" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H242" s="8" t="n"/>
+      <c r="I242" s="9" t="n"/>
+      <c r="J242" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K242" s="8" t="n"/>
+      <c r="L242" s="9" t="n"/>
+      <c r="M242" s="10" t="inlineStr">
+        <is>
+          <t>中等部・高等部共通。学校情報サイトのみで確認</t>
+        </is>
+      </c>
+      <c r="N242" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/2176</t>
+        </is>
+      </c>
+      <c r="O242" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="n">
+        <v>239</v>
+      </c>
+      <c r="B243" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>練馬区</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
+        <is>
+          <t>早稲田大学高等学院</t>
+        </is>
+      </c>
+      <c r="E243" s="6" t="inlineStr">
+        <is>
+          <t>03-5991-4156</t>
+        </is>
+      </c>
+      <c r="F243" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G243" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H243" s="8" t="n"/>
+      <c r="I243" s="9" t="n"/>
+      <c r="J243" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K243" s="8" t="n"/>
+      <c r="L243" s="9" t="n"/>
+      <c r="M243" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトの事務所の番号（「代表」の表記なし）。入試専用は03-5991-4210</t>
+        </is>
+      </c>
+      <c r="N243" s="11" t="inlineStr">
+        <is>
+          <t>https://www.waseda.jp/school/shs/access/</t>
+        </is>
+      </c>
+      <c r="O243" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="B244" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="C244" s="5" t="inlineStr">
+        <is>
+          <t>千代田区</t>
+        </is>
+      </c>
+      <c r="D244" s="5" t="inlineStr">
+        <is>
+          <t>和洋九段女子高等学校</t>
+        </is>
+      </c>
+      <c r="E244" s="6" t="inlineStr">
+        <is>
+          <t>03-3262-4161</t>
+        </is>
+      </c>
+      <c r="F244" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G244" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H244" s="8" t="n"/>
+      <c r="I244" s="9" t="n"/>
+      <c r="J244" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K244" s="8" t="n"/>
+      <c r="L244" s="9" t="n"/>
+      <c r="M244" s="10" t="inlineStr">
+        <is>
+          <t>中高共通</t>
+        </is>
+      </c>
+      <c r="N244" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inter-edu.com/schools/school/244</t>
+        </is>
+      </c>
+      <c r="O244" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O204"/>
-  <conditionalFormatting sqref="A5:O204">
+  <autoFilter ref="A4:O244"/>
+  <conditionalFormatting sqref="A5:O244">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="アポ獲得"</formula>
     </cfRule>
@@ -12491,10 +14839,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J244" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在・折返し待ち,担当者不在,資料送付,アポ獲得,検討中,NG,番号不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H204 K5:K204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H244 K5:K244" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -12699,6 +15047,46 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O202" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O203" r:id="rId199"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O204" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O205" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O206" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O207" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O208" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O209" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O210" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O211" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O215" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O217" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O218" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O219" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O220" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O221" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O222" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O223" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O224" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O225" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O226" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O227" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O228" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O229" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O230" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O231" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O232" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O233" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O234" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O235" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O236" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O237" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O238" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O239" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O240" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O241" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O242" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O243" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O244" r:id="rId240"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -12711,7 +15099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12798,43 +15186,43 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A4)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A4,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A4,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>B4-COUNTIFS('架電リスト'!$C$5:$C$204,A4,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A4,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B4-COUNTIFS('架電リスト'!$C$5:$C$244,A4,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A4,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A4,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A4,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A4,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A4,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A4,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A4,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H4" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A4,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A4,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I4" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A4,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A4,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J4" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A4,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A4,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K4" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A4,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A4,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -12845,43 +15233,43 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A5)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A5,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A5,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>B5-COUNTIFS('架電リスト'!$C$5:$C$204,A5,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A5,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B5-COUNTIFS('架電リスト'!$C$5:$C$244,A5,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A5,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A5,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A5,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A5,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A5,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A5,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A5,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A5,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A5,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A5,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A5,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A5,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A5,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A5,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A5,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -12892,43 +15280,43 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A6)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A6,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A6,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>B6-COUNTIFS('架電リスト'!$C$5:$C$204,A6,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A6,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B6-COUNTIFS('架電リスト'!$C$5:$C$244,A6,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A6,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A6,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A6,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A6,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A6,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A6,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A6,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A6,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A6,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A6,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A6,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A6,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A6,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A6,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A6,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -12939,1829 +15327,1923 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A7)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A7,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A7,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>B7-COUNTIFS('架電リスト'!$C$5:$C$204,A7,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A7,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B7-COUNTIFS('架電リスト'!$C$5:$C$244,A7,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A7,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A7,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A7,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A7,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A7,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A7,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A7,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A7,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A7,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A7,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A7,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A7,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A7,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A7,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A7,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>杉並区</t>
+          <t>豊島区</t>
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A8)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A8,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A8,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>B8-COUNTIFS('架電リスト'!$C$5:$C$204,A8,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A8,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B8-COUNTIFS('架電リスト'!$C$5:$C$244,A8,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A8,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A8,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A8,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A8,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A8,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A8,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A8,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A8,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A8,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A8,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A8,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J8" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A8,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A8,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A8,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A8,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>北区</t>
+          <t>杉並区</t>
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A9)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A9,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A9,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>B9-COUNTIFS('架電リスト'!$C$5:$C$204,A9,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A9,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B9-COUNTIFS('架電リスト'!$C$5:$C$244,A9,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A9,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A9,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A9,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A9,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A9,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A9,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A9,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A9,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A9,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A9,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A9,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J9" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A9,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A9,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A9,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A9,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>八王子市</t>
+          <t>北区</t>
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A10)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A10,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A10,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>B10-COUNTIFS('架電リスト'!$C$5:$C$204,A10,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A10,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B10-COUNTIFS('架電リスト'!$C$5:$C$244,A10,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A10,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A10,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A10,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A10,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A10,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A10,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A10,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A10,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A10,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A10,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A10,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J10" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A10,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A10,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A10,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A10,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>豊島区</t>
+          <t>八王子市</t>
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A11)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A11,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A11,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>B11-COUNTIFS('架電リスト'!$C$5:$C$204,A11,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A11,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B11-COUNTIFS('架電リスト'!$C$5:$C$244,A11,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A11,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A11,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A11,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A11,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A11,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A11,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A11,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A11,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A11,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A11,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A11,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J11" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A11,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A11,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A11,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A11,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>渋谷区</t>
+          <t>品川区</t>
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A12)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A12,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A12,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>B12-COUNTIFS('架電リスト'!$C$5:$C$204,A12,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A12,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B12-COUNTIFS('架電リスト'!$C$5:$C$244,A12,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A12,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A12,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A12,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A12,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A12,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A12,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A12,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A12,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A12,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A12,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A12,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J12" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A12,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A12,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A12,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A12,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>品川区</t>
+          <t>渋谷区</t>
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A13)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A13,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A13,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>B13-COUNTIFS('架電リスト'!$C$5:$C$204,A13,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A13,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B13-COUNTIFS('架電リスト'!$C$5:$C$244,A13,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A13,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A13,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A13,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A13,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A13,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A13,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A13,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A13,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A13,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A13,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A13,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J13" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A13,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A13,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A13,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A13,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>板橋区</t>
+          <t>中野区</t>
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A14)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A14,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A14,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>B14-COUNTIFS('架電リスト'!$C$5:$C$204,A14,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A14,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B14-COUNTIFS('架電リスト'!$C$5:$C$244,A14,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A14,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A14,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A14,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A14,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A14,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A14,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A14,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A14,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A14,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A14,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A14,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J14" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A14,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A14,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A14,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A14,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>大田区</t>
+          <t>新宿区</t>
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A15)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A15)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A15,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A15,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>B15-COUNTIFS('架電リスト'!$C$5:$C$204,A15,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A15,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B15-COUNTIFS('架電リスト'!$C$5:$C$244,A15,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A15,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A15,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A15,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A15,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A15,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A15,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A15,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A15,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A15,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A15,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A15,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J15" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A15,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A15,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A15,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A15,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>新宿区</t>
+          <t>目黒区</t>
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A16)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A16)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A16,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A16,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>B16-COUNTIFS('架電リスト'!$C$5:$C$204,A16,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A16,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B16-COUNTIFS('架電リスト'!$C$5:$C$244,A16,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A16,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A16,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A16,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A16,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A16,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A16,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A16,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A16,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A16,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A16,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A16,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A16,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A16,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A16,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A16,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>町田市</t>
+          <t>大田区</t>
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A17)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A17)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A17,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A17,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>B17-COUNTIFS('架電リスト'!$C$5:$C$204,A17,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A17,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B17-COUNTIFS('架電リスト'!$C$5:$C$244,A17,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A17,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A17,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A17,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A17,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A17,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A17,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A17,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A17,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A17,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A17,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A17,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A17,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A17,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A17,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A17,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>中野区</t>
+          <t>板橋区</t>
         </is>
       </c>
       <c r="B18" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A18)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A18)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A18,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A18,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>B18-COUNTIFS('架電リスト'!$C$5:$C$204,A18,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A18,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B18-COUNTIFS('架電リスト'!$C$5:$C$244,A18,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A18,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A18,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A18,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A18,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A18,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A18,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A18,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A18,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A18,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A18,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A18,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A18,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A18,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A18,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A18,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>江東区</t>
+          <t>町田市</t>
         </is>
       </c>
       <c r="B19" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A19)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A19)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A19,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A19,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>B19-COUNTIFS('架電リスト'!$C$5:$C$204,A19,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A19,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B19-COUNTIFS('架電リスト'!$C$5:$C$244,A19,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A19,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A19,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A19,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A19,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A19,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A19,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A19,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A19,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A19,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A19,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A19,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A19,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A19,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A19,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A19,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>武蔵野市</t>
+          <t>練馬区</t>
         </is>
       </c>
       <c r="B20" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A20)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A20)</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A20,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A20,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>B20-COUNTIFS('架電リスト'!$C$5:$C$204,A20,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A20,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B20-COUNTIFS('架電リスト'!$C$5:$C$244,A20,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A20,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A20,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A20,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A20,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A20,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A20,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A20,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A20,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A20,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A20,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A20,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J20" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A20,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A20,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A20,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A20,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>目黒区</t>
+          <t>江東区</t>
         </is>
       </c>
       <c r="B21" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A21)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A21)</f>
         <v/>
       </c>
       <c r="C21" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A21,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A21,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>B21-COUNTIFS('架電リスト'!$C$5:$C$204,A21,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A21,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B21-COUNTIFS('架電リスト'!$C$5:$C$244,A21,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A21,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A21,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A21,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A21,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A21,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A21,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A21,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A21,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A21,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A21,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A21,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J21" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A21,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A21,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A21,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A21,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>江戸川区</t>
+          <t>武蔵野市</t>
         </is>
       </c>
       <c r="B22" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A22)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A22)</f>
         <v/>
       </c>
       <c r="C22" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A22,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A22,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>B22-COUNTIFS('架電リスト'!$C$5:$C$204,A22,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A22,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B22-COUNTIFS('架電リスト'!$C$5:$C$244,A22,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A22,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A22,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A22,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A22,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A22,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A22,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A22,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A22,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A22,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A22,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A22,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A22,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A22,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A22,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A22,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>国立市</t>
+          <t>調布市</t>
         </is>
       </c>
       <c r="B23" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A23)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A23)</f>
         <v/>
       </c>
       <c r="C23" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A23,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A23,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>B23-COUNTIFS('架電リスト'!$C$5:$C$204,A23,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A23,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B23-COUNTIFS('架電リスト'!$C$5:$C$244,A23,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A23,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A23,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A23,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A23,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A23,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A23,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A23,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A23,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A23,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A23,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A23,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J23" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A23,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A23,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A23,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A23,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>小平市</t>
+          <t>江戸川区</t>
         </is>
       </c>
       <c r="B24" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A24)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A24)</f>
         <v/>
       </c>
       <c r="C24" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A24,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A24,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>B24-COUNTIFS('架電リスト'!$C$5:$C$204,A24,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A24,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B24-COUNTIFS('架電リスト'!$C$5:$C$244,A24,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A24,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A24,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A24,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A24,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A24,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A24,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A24,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A24,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A24,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A24,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A24,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J24" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A24,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A24,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A24,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A24,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>調布市</t>
+          <t>国立市</t>
         </is>
       </c>
       <c r="B25" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A25)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A25)</f>
         <v/>
       </c>
       <c r="C25" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A25,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A25,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>B25-COUNTIFS('架電リスト'!$C$5:$C$204,A25,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A25,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B25-COUNTIFS('架電リスト'!$C$5:$C$244,A25,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A25,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A25,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A25,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A25,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A25,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A25,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A25,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A25,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A25,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A25,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A25,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J25" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A25,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A25,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A25,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A25,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>小金井市</t>
+          <t>小平市</t>
         </is>
       </c>
       <c r="B26" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A26)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A26)</f>
         <v/>
       </c>
       <c r="C26" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A26,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A26,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D26" s="16">
-        <f>B26-COUNTIFS('架電リスト'!$C$5:$C$204,A26,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A26,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B26-COUNTIFS('架電リスト'!$C$5:$C$244,A26,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A26,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E26" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A26,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A26,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A26,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A26,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G26" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A26,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A26,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A26,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A26,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A26,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A26,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J26" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A26,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A26,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A26,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A26,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>足立区</t>
+          <t>小金井市</t>
         </is>
       </c>
       <c r="B27" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A27)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A27)</f>
         <v/>
       </c>
       <c r="C27" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A27,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A27,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>B27-COUNTIFS('架電リスト'!$C$5:$C$204,A27,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A27,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B27-COUNTIFS('架電リスト'!$C$5:$C$244,A27,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A27,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A27,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A27,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A27,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A27,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G27" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A27,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A27,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A27,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A27,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A27,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A27,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J27" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A27,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A27,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A27,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A27,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>台東区</t>
+          <t>三鷹市</t>
         </is>
       </c>
       <c r="B28" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A28)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A28)</f>
         <v/>
       </c>
       <c r="C28" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A28,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A28,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D28" s="16">
-        <f>B28-COUNTIFS('架電リスト'!$C$5:$C$204,A28,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A28,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B28-COUNTIFS('架電リスト'!$C$5:$C$244,A28,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A28,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E28" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A28,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A28,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A28,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A28,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A28,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A28,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A28,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A28,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A28,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A28,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J28" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A28,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A28,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K28" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A28,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A28,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>練馬区</t>
+          <t>東村山市</t>
         </is>
       </c>
       <c r="B29" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A29)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A29)</f>
         <v/>
       </c>
       <c r="C29" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A29,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A29,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D29" s="16">
-        <f>B29-COUNTIFS('架電リスト'!$C$5:$C$204,A29,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A29,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B29-COUNTIFS('架電リスト'!$C$5:$C$244,A29,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A29,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E29" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A29,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A29,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A29,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A29,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G29" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A29,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A29,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A29,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A29,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A29,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A29,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J29" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A29,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A29,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K29" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A29,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A29,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>多摩市</t>
+          <t>墨田区</t>
         </is>
       </c>
       <c r="B30" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A30)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A30)</f>
         <v/>
       </c>
       <c r="C30" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A30,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A30,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D30" s="16">
-        <f>B30-COUNTIFS('架電リスト'!$C$5:$C$204,A30,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A30,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B30-COUNTIFS('架電リスト'!$C$5:$C$244,A30,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A30,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E30" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A30,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A30,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A30,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A30,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G30" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A30,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A30,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A30,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A30,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A30,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A30,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J30" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A30,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A30,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K30" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A30,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A30,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>荒川区</t>
+          <t>足立区</t>
         </is>
       </c>
       <c r="B31" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A31)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A31)</f>
         <v/>
       </c>
       <c r="C31" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A31,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A31,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D31" s="16">
-        <f>B31-COUNTIFS('架電リスト'!$C$5:$C$204,A31,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A31,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B31-COUNTIFS('架電リスト'!$C$5:$C$244,A31,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A31,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E31" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A31,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A31,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F31" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A31,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A31,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G31" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A31,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A31,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A31,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A31,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I31" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A31,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A31,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J31" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A31,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A31,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K31" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A31,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A31,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>葛飾区</t>
+          <t>台東区</t>
         </is>
       </c>
       <c r="B32" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A32)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A32)</f>
         <v/>
       </c>
       <c r="C32" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A32,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A32,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D32" s="16">
-        <f>B32-COUNTIFS('架電リスト'!$C$5:$C$204,A32,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A32,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B32-COUNTIFS('架電リスト'!$C$5:$C$244,A32,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A32,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E32" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A32,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A32,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F32" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A32,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A32,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G32" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A32,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A32,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H32" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A32,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A32,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I32" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A32,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A32,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J32" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A32,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A32,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K32" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A32,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A32,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>立川市</t>
+          <t>多摩市</t>
         </is>
       </c>
       <c r="B33" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A33)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A33)</f>
         <v/>
       </c>
       <c r="C33" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A33,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A33,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D33" s="16">
-        <f>B33-COUNTIFS('架電リスト'!$C$5:$C$204,A33,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A33,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B33-COUNTIFS('架電リスト'!$C$5:$C$244,A33,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A33,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E33" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A33,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A33,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F33" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A33,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A33,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G33" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A33,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A33,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H33" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A33,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A33,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I33" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A33,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A33,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J33" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A33,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A33,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K33" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A33,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A33,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>中央区</t>
+          <t>荒川区</t>
         </is>
       </c>
       <c r="B34" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A34)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A34)</f>
         <v/>
       </c>
       <c r="C34" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A34,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A34,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D34" s="16">
-        <f>B34-COUNTIFS('架電リスト'!$C$5:$C$204,A34,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A34,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B34-COUNTIFS('架電リスト'!$C$5:$C$244,A34,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A34,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E34" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A34,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A34,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F34" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A34,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A34,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G34" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A34,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A34,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H34" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A34,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A34,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I34" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A34,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A34,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J34" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A34,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A34,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K34" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A34,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A34,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>昭島市</t>
+          <t>葛飾区</t>
         </is>
       </c>
       <c r="B35" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A35)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A35)</f>
         <v/>
       </c>
       <c r="C35" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A35,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A35,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D35" s="16">
-        <f>B35-COUNTIFS('架電リスト'!$C$5:$C$204,A35,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A35,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B35-COUNTIFS('架電リスト'!$C$5:$C$244,A35,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A35,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E35" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A35,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A35,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F35" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A35,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A35,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G35" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A35,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A35,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H35" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A35,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A35,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I35" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A35,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A35,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J35" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A35,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A35,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K35" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A35,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A35,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
         <is>
-          <t>稲城市</t>
+          <t>立川市</t>
         </is>
       </c>
       <c r="B36" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A36)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A36)</f>
         <v/>
       </c>
       <c r="C36" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A36,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A36,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D36" s="16">
-        <f>B36-COUNTIFS('架電リスト'!$C$5:$C$204,A36,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A36,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B36-COUNTIFS('架電リスト'!$C$5:$C$244,A36,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A36,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E36" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A36,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A36,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F36" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A36,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A36,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G36" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A36,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A36,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H36" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A36,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A36,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I36" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A36,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A36,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J36" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A36,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A36,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K36" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A36,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A36,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>東久留米市</t>
+          <t>西東京市</t>
         </is>
       </c>
       <c r="B37" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A37)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A37)</f>
         <v/>
       </c>
       <c r="C37" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A37,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A37,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D37" s="16">
-        <f>B37-COUNTIFS('架電リスト'!$C$5:$C$204,A37,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A37,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B37-COUNTIFS('架電リスト'!$C$5:$C$244,A37,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A37,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E37" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A37,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A37,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F37" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A37,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A37,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G37" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A37,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A37,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H37" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A37,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A37,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I37" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A37,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A37,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J37" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A37,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A37,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K37" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A37,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A37,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>三鷹市</t>
+          <t>中央区</t>
         </is>
       </c>
       <c r="B38" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A38)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A38)</f>
         <v/>
       </c>
       <c r="C38" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A38,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A38,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D38" s="16">
-        <f>B38-COUNTIFS('架電リスト'!$C$5:$C$204,A38,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A38,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B38-COUNTIFS('架電リスト'!$C$5:$C$244,A38,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A38,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E38" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A38,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A38,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F38" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A38,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A38,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G38" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A38,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A38,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H38" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A38,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A38,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I38" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A38,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A38,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J38" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A38,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A38,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K38" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A38,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A38,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>武蔵村山市</t>
+          <t>昭島市</t>
         </is>
       </c>
       <c r="B39" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A39)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A39)</f>
         <v/>
       </c>
       <c r="C39" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A39,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A39,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D39" s="16">
-        <f>B39-COUNTIFS('架電リスト'!$C$5:$C$204,A39,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A39,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B39-COUNTIFS('架電リスト'!$C$5:$C$244,A39,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A39,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E39" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A39,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A39,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F39" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A39,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A39,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G39" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A39,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A39,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H39" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A39,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A39,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I39" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A39,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A39,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J39" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A39,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A39,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K39" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A39,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A39,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>あきる野市</t>
+          <t>稲城市</t>
         </is>
       </c>
       <c r="B40" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A40)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A40)</f>
         <v/>
       </c>
       <c r="C40" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A40,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A40,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D40" s="16">
-        <f>B40-COUNTIFS('架電リスト'!$C$5:$C$204,A40,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A40,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B40-COUNTIFS('架電リスト'!$C$5:$C$244,A40,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A40,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E40" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A40,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A40,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F40" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A40,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A40,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G40" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A40,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A40,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H40" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A40,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A40,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I40" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A40,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A40,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J40" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A40,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A40,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K40" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A40,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A40,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>西東京市</t>
+          <t>東久留米市</t>
         </is>
       </c>
       <c r="B41" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A41)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A41)</f>
         <v/>
       </c>
       <c r="C41" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A41,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A41,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D41" s="16">
-        <f>B41-COUNTIFS('架電リスト'!$C$5:$C$204,A41,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A41,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B41-COUNTIFS('架電リスト'!$C$5:$C$244,A41,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A41,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E41" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A41,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A41,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F41" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A41,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A41,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G41" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A41,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A41,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H41" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A41,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A41,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I41" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A41,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A41,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J41" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A41,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A41,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K41" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A41,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A41,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>清瀬市</t>
+          <t>武蔵村山市</t>
         </is>
       </c>
       <c r="B42" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A42)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A42)</f>
         <v/>
       </c>
       <c r="C42" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A42,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A42,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D42" s="16">
-        <f>B42-COUNTIFS('架電リスト'!$C$5:$C$204,A42,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A42,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B42-COUNTIFS('架電リスト'!$C$5:$C$244,A42,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A42,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E42" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A42,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A42,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F42" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A42,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A42,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G42" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A42,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A42,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H42" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A42,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A42,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I42" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A42,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A42,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J42" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A42,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A42,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K42" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A42,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A42,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>東村山市</t>
+          <t>あきる野市</t>
         </is>
       </c>
       <c r="B43" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A43)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A43)</f>
         <v/>
       </c>
       <c r="C43" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A43,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A43,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D43" s="16">
-        <f>B43-COUNTIFS('架電リスト'!$C$5:$C$204,A43,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A43,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B43-COUNTIFS('架電リスト'!$C$5:$C$244,A43,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A43,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E43" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A43,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A43,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F43" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A43,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A43,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G43" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A43,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A43,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H43" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A43,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A43,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I43" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A43,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A43,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J43" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A43,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A43,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K43" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A43,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A43,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>墨田区</t>
+          <t>清瀬市</t>
         </is>
       </c>
       <c r="B44" s="16">
-        <f>COUNTIF('架電リスト'!$C$5:$C$204,A44)</f>
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A44)</f>
         <v/>
       </c>
       <c r="C44" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,A44,'架電リスト'!$E$5:$E$204,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A44,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D44" s="16">
-        <f>B44-COUNTIFS('架電リスト'!$C$5:$C$204,A44,'架電リスト'!$J$5:$J$204,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$204,A44,'架電リスト'!$J$5:$J$204,"")</f>
+        <f>B44-COUNTIFS('架電リスト'!$C$5:$C$244,A44,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A44,'架電リスト'!$J$5:$J$244,"")</f>
         <v/>
       </c>
       <c r="E44" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A44,'架電リスト'!$J$5:$J$204,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A44,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F44" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A44,'架電リスト'!$J$5:$J$204,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A44,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
         <v/>
       </c>
       <c r="G44" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A44,'架電リスト'!$J$5:$J$204,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A44,'架電リスト'!$J$5:$J$244,"資料送付")</f>
         <v/>
       </c>
       <c r="H44" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A44,'架電リスト'!$J$5:$J$204,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A44,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I44" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A44,'架電リスト'!$J$5:$J$204,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A44,'架電リスト'!$J$5:$J$244,"検討中")</f>
         <v/>
       </c>
       <c r="J44" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A44,'架電リスト'!$J$5:$J$204,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A44,'架電リスト'!$J$5:$J$244,"NG")</f>
         <v/>
       </c>
       <c r="K44" s="16">
-        <f>COUNTIFS('架電リスト'!$C$5:$C$204,$A44,'架電リスト'!$J$5:$J$204,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A44,'架電リスト'!$J$5:$J$244,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>府中市</t>
+        </is>
+      </c>
+      <c r="B45" s="16">
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A45)</f>
+        <v/>
+      </c>
+      <c r="C45" s="16">
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A45,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D45" s="16">
+        <f>B45-COUNTIFS('架電リスト'!$C$5:$C$244,A45,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A45,'架電リスト'!$J$5:$J$244,"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="16">
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A45,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
+        <v/>
+      </c>
+      <c r="F45" s="16">
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A45,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
+        <v/>
+      </c>
+      <c r="G45" s="16">
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A45,'架電リスト'!$J$5:$J$244,"資料送付")</f>
+        <v/>
+      </c>
+      <c r="H45" s="16">
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A45,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
+        <v/>
+      </c>
+      <c r="I45" s="16">
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A45,'架電リスト'!$J$5:$J$244,"検討中")</f>
+        <v/>
+      </c>
+      <c r="J45" s="16">
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A45,'架電リスト'!$J$5:$J$244,"NG")</f>
+        <v/>
+      </c>
+      <c r="K45" s="16">
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A45,'架電リスト'!$J$5:$J$244,"番号不明")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>国分寺市</t>
+        </is>
+      </c>
+      <c r="B46" s="16">
+        <f>COUNTIF('架電リスト'!$C$5:$C$244,A46)</f>
+        <v/>
+      </c>
+      <c r="C46" s="16">
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,A46,'架電リスト'!$E$5:$E$244,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D46" s="16">
+        <f>B46-COUNTIFS('架電リスト'!$C$5:$C$244,A46,'架電リスト'!$J$5:$J$244,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$244,A46,'架電リスト'!$J$5:$J$244,"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="16">
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A46,'架電リスト'!$J$5:$J$244,"不在・折返し待ち")</f>
+        <v/>
+      </c>
+      <c r="F46" s="16">
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A46,'架電リスト'!$J$5:$J$244,"担当者不在")</f>
+        <v/>
+      </c>
+      <c r="G46" s="16">
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A46,'架電リスト'!$J$5:$J$244,"資料送付")</f>
+        <v/>
+      </c>
+      <c r="H46" s="16">
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A46,'架電リスト'!$J$5:$J$244,"アポ獲得")</f>
+        <v/>
+      </c>
+      <c r="I46" s="16">
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A46,'架電リスト'!$J$5:$J$244,"検討中")</f>
+        <v/>
+      </c>
+      <c r="J46" s="16">
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A46,'架電リスト'!$J$5:$J$244,"NG")</f>
+        <v/>
+      </c>
+      <c r="K46" s="16">
+        <f>COUNTIFS('架電リスト'!$C$5:$C$244,$A46,'架電リスト'!$J$5:$J$244,"番号不明")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B45" s="17">
-        <f>SUM(B4:B44)</f>
-        <v/>
-      </c>
-      <c r="C45" s="17">
-        <f>SUM(C4:C44)</f>
-        <v/>
-      </c>
-      <c r="D45" s="17">
-        <f>SUM(D4:D44)</f>
-        <v/>
-      </c>
-      <c r="E45" s="17">
-        <f>SUM(E4:E44)</f>
-        <v/>
-      </c>
-      <c r="F45" s="17">
-        <f>SUM(F4:F44)</f>
-        <v/>
-      </c>
-      <c r="G45" s="17">
-        <f>SUM(G4:G44)</f>
-        <v/>
-      </c>
-      <c r="H45" s="17">
-        <f>SUM(H4:H44)</f>
-        <v/>
-      </c>
-      <c r="I45" s="17">
-        <f>SUM(I4:I44)</f>
-        <v/>
-      </c>
-      <c r="J45" s="17">
-        <f>SUM(J4:J44)</f>
-        <v/>
-      </c>
-      <c r="K45" s="17">
-        <f>SUM(K4:K44)</f>
+      <c r="B47" s="17">
+        <f>SUM(B4:B46)</f>
+        <v/>
+      </c>
+      <c r="C47" s="17">
+        <f>SUM(C4:C46)</f>
+        <v/>
+      </c>
+      <c r="D47" s="17">
+        <f>SUM(D4:D46)</f>
+        <v/>
+      </c>
+      <c r="E47" s="17">
+        <f>SUM(E4:E46)</f>
+        <v/>
+      </c>
+      <c r="F47" s="17">
+        <f>SUM(F4:F46)</f>
+        <v/>
+      </c>
+      <c r="G47" s="17">
+        <f>SUM(G4:G46)</f>
+        <v/>
+      </c>
+      <c r="H47" s="17">
+        <f>SUM(H4:H46)</f>
+        <v/>
+      </c>
+      <c r="I47" s="17">
+        <f>SUM(I4:I46)</f>
+        <v/>
+      </c>
+      <c r="J47" s="17">
+        <f>SUM(J4:J46)</f>
+        <v/>
+      </c>
+      <c r="K47" s="17">
+        <f>SUM(K4:K46)</f>
         <v/>
       </c>
     </row>
@@ -14851,7 +17333,7 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・東京都、200校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
+          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・東京都、240校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
         </is>
       </c>
     </row>
